--- a/assets/xlsx/testing.xlsx
+++ b/assets/xlsx/testing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\migrasiplaywright12345\assets\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\automationtestingjudges\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1891C57-40E2-4AAA-A14D-4F4E7EFE18A8}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C877B567-2A02-47EC-9375-759DAEFD79BA}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,13 +42,13 @@
     <t>Apa itu asuransi jiwa</t>
   </si>
   <si>
-    <t>Jenis asuransi ini memberikan perlindungan finansial terhadap risiko kehidupan dan kematian pemegang polis.</t>
-  </si>
-  <si>
     <t>Apa itu asuransi kesehatan</t>
   </si>
   <si>
     <t>Asuransi kesehatan merupakan jenis asuransi yang memberikan perlindungan finansial ketika mengalami masalah kesehatan.</t>
+  </si>
+  <si>
+    <t>HIDUP JOKOWI!!</t>
   </si>
 </sst>
 </file>
@@ -521,7 +521,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -529,13 +529,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/assets/xlsx/testing.xlsx
+++ b/assets/xlsx/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMG\Documents\GITHUB\automationtestingjudges\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1546FF77-86D7-4033-AF94-05807C25BB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279DFE6E-02F6-4810-9925-9CD1A5FFCF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
   <si>
     <t>No</t>
   </si>
@@ -34,56 +34,408 @@
     <t>Context</t>
   </si>
   <si>
-    <t>Apa itu Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Omnibotika V2 adalah sebuah dashboard layanan pelanggan yang dirancang untuk mengumpulkan semua pesan dari berbagai saluran komunikasi seperti WhatsApp, Facebook Messenger, Instagram, LINE, Telegram, Shopee, Lazada, dan lain-lain ke dalam satu tampilan. Dengan Omnibotika V2, tim Customer Service (CS) tidak perlu membuka banyak aplikasi berbeda. Semua pesan pelanggan bisa dibaca, dijawab, dan dipantau langsung dari satu dashboard.</t>
-  </si>
-  <si>
-    <t>Apa fungsi menu Home di Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Menu Home di Omnibotika V2 berfungsi sebagai halaman utama yang menampilkan ringkasan aktivitas layanan hari ini. Di sini Anda bisa melihat jumlah tiket berdasarkan status (New, Open, Hold, Solved, dll), SLA (Service Level Agreement), agen yang sedang online, tingkat kepuasan pelanggan (CSAT), serta channel komunikasi yang paling aktif digunakan pelanggan hari ini. Menu ini cocok untuk supervisor yang ingin memantau kondisi tim secara sekilas.</t>
-  </si>
-  <si>
-    <t>Apa itu Total Tickets Received di Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Total Tickets Received di Omnibotika V2 adalah jumlah tiket yang diterima sistem dalam rentang waktu tertentu. Angka ini memberikan gambaran beban kerja tim Customer Service dan bisa digunakan untuk menganalisis tren pertanyaan atau keluhan pelanggan dari waktu ke waktu.</t>
-  </si>
-  <si>
-    <t>Apa fungsi Wallboard di Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Wallboard di Omnibotika V2 adalah tampilan visual berbentuk dashboard besar yang menampilkan data layanan pelanggan secara real-time, seperti jumlah tiket baru, status tiket, SLA, agen online, dan kepuasan pelanggan (CSAT). Biasanya fitur ini digunakan supervisor atau manajer untuk memantau performa tim secara langsung.</t>
-  </si>
-  <si>
-    <t>fungsi home</t>
-  </si>
-  <si>
-    <t>fungsi wallboard</t>
-  </si>
-  <si>
-    <t>ticke received</t>
-  </si>
-  <si>
-    <t>omnibotika</t>
-  </si>
-  <si>
-    <t>aku mau daftar asuransi</t>
-  </si>
-  <si>
-    <t>Mohon maaf, Luna tidak bisa menjawab pertanyaan Anda.</t>
-  </si>
-  <si>
-    <t>Unkown</t>
+    <t>Lokasi Kantor Botika</t>
+  </si>
+  <si>
+    <t>Kantor Botika ada di mana sih?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAD OFFICE
+Jl Perumnas Blok E III No 50
+Seturan Yogyakarta
+TECHNICAL OFFICE
+Yunion Space, Agres ID Lt 3,
+Jl. C. Simanjuntak No.101, Terban, Kec. Gondokusuman, Kota Yogyakarta, Daerah Istimewa Yogyakarta 55223
+</t>
+  </si>
+  <si>
+    <t>Jam Layanan Botika</t>
+  </si>
+  <si>
+    <t>Botika buka kapan aja?</t>
+  </si>
+  <si>
+    <t>Opening Hour
+Monday – Friday: 8.30 WIB – 17.00 WIB
+Saturday – Sunday: Libur</t>
+  </si>
+  <si>
+    <t>Kontak Botika</t>
+  </si>
+  <si>
+    <t>Gimana cara menghubungi Botika?</t>
+  </si>
+  <si>
+    <t>Email
+support@botika.online
+Call Service
++6288978001099 (Call Only)
++6281802207000 (Whatsapp Only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Siapa Botika?
+Botika Itu Apa</t>
+  </si>
+  <si>
+    <t>Botika itu apa sih?</t>
+  </si>
+  <si>
+    <t>Perusahan dengan teknologi kecerdasan buatan yang mampu melakukan pembelajaran mesin (machine learning) dan pemrosesan bahasa alamiah (natural language processing (NLP)) atas bahasa lokal, sehingga memudahkan para pelaku bisnis untuk melayani sejumlah besar pelanggan dan mengurangi biaya, namun di saat yang sama meningkatkan kualitas pelayanan.</t>
+  </si>
+  <si>
+    <t>Teknologi Kami</t>
+  </si>
+  <si>
+    <t>Teknologi apa yang dipakai Botika?</t>
+  </si>
+  <si>
+    <t>Botika menawarkan chatbot berbasis AI dan omnichannel dashboard yang memudahkan pelaku bisnis menangani konsumen. Teknologi kami mengerti apa kebutuhan Anda dan memiliki kemampuan otomotis untuk: melakukan pekerjaan-pekerjaan repetitif, melakukan percakapan, bertransaksi dan bercakap-cakap secara intelektual baik dengan pelanggan dalam bentuk teks atau suara dalam berbagai media seperti e-mail, Whatsapp, LINE, Messenger, Telegram, website, aplikasi mobile, dan lain-lain.</t>
+  </si>
+  <si>
+    <t>Untuk menjalin kerjasama dan kesempatan investasi
+(Bagaimana cara menjalin kerjasama dan menemukan kesmepatan investasi?)</t>
+  </si>
+  <si>
+    <t>Gimana cara kerjasama atau investasi di Botika?</t>
+  </si>
+  <si>
+    <t>hubungi kami melalui admin@botika.online
+(Untuk menjalin kerjasama atau mengeksplorasi peluang investasi, silakan hubungi kami di admin@botika.online.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertarik dengan AI/Machine Learning?
+</t>
+  </si>
+  <si>
+    <t>Pengen kerja di tim AI/Machine Learning Botika?</t>
+  </si>
+  <si>
+    <t>Bergabunglah dengan tim kami yang terus berkembang 🚀
+Kami membuka kesempatan untuk bergabung melalui:
+• Program Magang
+• Lowongan Kerja 
+Silakan kirimkan CV dan dokumen pendukung Anda ke:
+📧 hrd@botika.online
+Gunakan subject email:
+[Magang / Posisi yang Dilamar] – [Nama Lengkap]
+Kami menantikan talenta terbaik untuk berkembang bersama kami di industri Artificial Intelligence.</t>
+  </si>
+  <si>
+    <t>Visi misi</t>
+  </si>
+  <si>
+    <t>Apa visi dan misi Botika?</t>
+  </si>
+  <si>
+    <t>Misi
+Menyediakan asisten AI yang bisa berinteraksi baik dalam teks maupun suara menggunakan channel komunikasi moderen
+Visi
+Kecerdasan buartan untuk melayani kebutuhan manusia</t>
+  </si>
+  <si>
+    <t>Pasar internasional yang menggunakan layanan Botika</t>
+  </si>
+  <si>
+    <t>Botika udah dipakai di negara mana aja?</t>
+  </si>
+  <si>
+    <t>Indonesia, Malaysia, Singapore, Philippines, Thailand, Bangladesh, Vietnam, Cambodia, South Korea, Japan, Taiwan, South China, North and East China.</t>
+  </si>
+  <si>
+    <t>Road Map Botika</t>
+  </si>
+  <si>
+    <t>Gimana roadmap perkembangan Botika?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017
+Chatbot
+Text based conversational AI for social media : whatsapp, facebook, instagram, twitter, line, telegram, livechat, email
+2018
+Omnibotika
+is a all in one dashboard to help customer services in serving consumers to achieve target and help you to satisfy your consumers.
+2018
+Text to Speech
+Text to speech and speech to text, creating voice with natural neural network technology.
+2018
+Speech to Text
+can be integrated with artificial intelligence, so that it can simplify our daily activities.
+2019
+Voice Botika
+For creating Chatbot &amp; Voicebot using Botika engine
+2019
+Smart Speaker
+can be integrated with artificial intelligence, so that it can simplify our daily activities
+2020
+Platform
+An all-in-one platform to build and launch conversational chatbots without coding.
+2021
+VB App
+VB is an application with the “Luna” bot and Indonesian text to speech technology with two voice options
+2022
+Wabis Botika
+is a platform to upgrade you whatsapp business to whatsapp business API with masking name and green thick
+</t>
+  </si>
+  <si>
+    <t>Botika teknologi</t>
+  </si>
+  <si>
+    <t>Teknologi apa aja yang ada di Botika?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEXT
+POS Tagging
+Sentence Boundaries
+Text Chunking
+Syntax Analysis
+Language Modeling
+Question Answering
+Intent Classification
+Named Entity Recognition (NER)
+Topic Detection
+Text Summarization
+Text Generation
+Word Tokenization
+TEXT &amp; VOICE 
+Speech Recognition(STT) 
+Speech Synthesizing (TTS) 
+COMPUTER VISION
+OCR 
+Image Classification 
+Face Recognition 
+</t>
+  </si>
+  <si>
+    <t>Competitive Advantage</t>
+  </si>
+  <si>
+    <t>Apa keunggulan Botika dibanding yang lain?</t>
+  </si>
+  <si>
+    <t>Kombinasi Chatbot dan Omni Channel
+Kolaborasi manusia dengan mesin. Chatbot dapat mengeskalasi kasus kepada agen untuk sentuhan manusia dan penyelesaian masalah yang kompleks.
+Teknologi Suara Internal
+Speech To Text dan Text To Voice untuk memungkinkan komunikasi berbasis suara untuk speaker pintar dan telepon.
+Terhubung dengan Sistem yang Ada Melalui API dengan Mulus
+Menghubungkan sistem yang ada ke chatbot untuk bertransaksi dengan pelanggan dan mendapatkan data yang relevan.
+Sangat Dapat Disesuaikan
+Dengan mudah membuat persona chatbot dan karakter suara yang sesuai dengan merek dan target pasar.
+Pengiriman Cepat
+Waktu rata-rata untuk pengembangan khusus hingga rilis versi kurang dari 4 minggu.
+Harga Kompetitif, Layanan Unggul
+NLP dan Pembelajaran Mesin Internal dalam Bahasa Lokal Mesin internal yang dibangun untuk memastikan inovasi cepat dan fleksibilitas dalam melayani pelanggan dalam bahasa mereka.</t>
+  </si>
+  <si>
+    <t>Team Member</t>
+  </si>
+  <si>
+    <t>Siapa aja tim di balik Botika?</t>
+  </si>
+  <si>
+    <t>Ide BOTIKA dimulai pada tanggal 1 September 2016 oleh dua pemuda dari Yogyakarta, Dito Anindita dan Galuh Koco Sadewo.
+Untuk mewujudkan ide ini, mereka juga berkolaborasi dengan Prima Kharisma, Eri Kuncoro, dan Vita Subiyakti untuk membuat terobosan dalam teknologi AI di Indonesia.
+Dengan ini, mereka percaya bahwa teknologi AI mampu menyederhanakan setiap aspek kehidupan manusia.
+Sekarang Botika sudah memiliki 50 karyawan yang tersebar di Yogyakarta dan Jakarta</t>
+  </si>
+  <si>
+    <t>Informasi magang/pkl</t>
+  </si>
+  <si>
+    <t>Ada info magang/PKL nggak?</t>
+  </si>
+  <si>
+    <t>Untuk informasi magang/pkl dapat menghubungi kami melalui email hrd@botika.online</t>
+  </si>
+  <si>
+    <t>apakah ada lowongan pekerjaan</t>
+  </si>
+  <si>
+    <t>Ada lowongan kerja nggak di Botika?</t>
+  </si>
+  <si>
+    <t>Untuk menjalin kerjasama dan kesempatan investasi</t>
+  </si>
+  <si>
+    <t>Mau tawarin kios atau layanan ke Botika, gimana caranya?</t>
+  </si>
+  <si>
+    <t>Produk Business and Partnership di Botika berfokus pada pembangunan kerja sama strategis dengan berbagai pihak untuk memperluas peluang bisnis dan menciptakan nilai bersama.
+Melalui program ini, Botika membuka kesempatan bagi perusahaan, lembaga, maupun individu untuk menjalin kemitraan bisnis, kolaborasi teknologi, atau kerja sama komersial yang saling menguntungkan.
+Setiap bentuk kerja sama akan disesuaikan dengan kebutuhan dan tujuan masing-masing mitra, dengan fokus pada pengembangan bisnis, inovasi produk, dan peningkatan efisiensi operasional.
+Jika Anda tertarik menjalin kerja sama atau ingin mengeksplorasi peluang kemitraan dan investasi, silakan hubungi kami melalui email di galuh@botika.online</t>
+  </si>
+  <si>
+    <t>Apa saja produk di Botika?</t>
+  </si>
+  <si>
+    <t>Mau proposal kerjasama, emailnya ke mana?</t>
+  </si>
+  <si>
+    <t>Produk produk di botika antara lain, LLM, Digital Human AI (Virtual Avatar), Omnibotika, Voicebotika, Blastika, Chatbotika, Platform, Wabis (Whatsapp Business). Untuk penjelasan produk lebih lanjut silakan kunjungi https://botika.online/product</t>
+  </si>
+  <si>
+    <t>Portofolio Botika</t>
+  </si>
+  <si>
+    <t>Produk apa aja sih yang ada di Botika?</t>
+  </si>
+  <si>
+    <t>Untuk melihat portofolio Botika, silakan kunjungi https://botika.online/. Di sana, terdapat penjelasan singkat mengenai produk-produk kami dan berbagai use case dari tiap klien yang telah menggunakan layanan Botika.</t>
+  </si>
+  <si>
+    <t>berapa SLA yang diperlukan, khususnya untuk perubahan mendadak (misalnya, d</t>
+  </si>
+  <si>
+    <t>Portofolio Botika bisa dilihat di mana?</t>
+  </si>
+  <si>
+    <t>Untuk perubahan ini nanti akan berbeda-beda untuk timelinenya bergantung dengan seberapa banyak yang perlu diubah dan apakah masuk ke Mayor, Medium, Minor. Untuk lebih jelasnya dapat mengikuti panduan SLA dibawha ini ;</t>
+  </si>
+  <si>
+    <t>Siapa kamu?
+Kamu itu siapa?
+Perkenalkan dirimu
+Luna siapanya botika</t>
+  </si>
+  <si>
+    <t>SLA-nya gimana tuh kalau ada perubahan?</t>
+  </si>
+  <si>
+    <t>Perkenalkan, saya Luna, asisten virtual dari Botika. Saya siap membantu menjawab pertanyaan seputar produk Botika, mengatasi kendala yang Anda alami, serta menjawab pertanyaan umum lainnya. Jangan ragu untuk bertanya, saya selalu tersedia untuk Anda.</t>
+  </si>
+  <si>
+    <t>Penghargaan Botika
+Pencapaian terbesar Botika</t>
+  </si>
+  <si>
+    <t>Kamu ini siapa sih?</t>
+  </si>
+  <si>
+    <t>Berikut pencapaian terbesar yang telah diraih dan penghargaan industri yang diterima Botika atas solusi AI-nya yang inovatif:
+- 2024 (Microsoft BUILD: AI Day)
+Awards/Achievement: KAI partner for digital human AI
+Products: Superchatbot &amp; Digital Human AI botika: Nilam KAI
+Descriptions: Microsoft Chairman and CEO, Satya Nadella, visited Indonesia to meet with Microsoft partners utilizing AI technology in everyday applications. As part of this visit, Botika was highlighted for its collaboration with Microsoft in developing a digital human AI for KAI, demonstrating the innovative integration of AI into real-world solutions.
+- 2023 (Microsoft Generative AI Champion 2023)
+Awards/Achievement: Microsoft Indonesia Partner Award
+Products: Superchatbot &amp; Digital Human AI Botika
+Descriptions: Reaching New Heights with Generative AI! We are proud to announce that Botika has been named a Generative AI Champion Partner at the FY 24 Microsoft Indonesia Kick Off event, themed 'Empowering Growth and Innovation in Indonesia.' The event, held at Glass House, Ritz Carlton Pacific Place, Jakarta, reaffirms our commitment to driving growth and innovation in the country.The award was presented by Microsoft Indonesia President Director, Darma Simorangkir, to Galuh Koco Sadewo, Co-Founder &amp; CBD of Botika Teknologi. We believe Generative AI will revolutionize the business and communication landscape, and together with Microsoft, we will continue delivering advanced solutions to help Indonesian businesses grow and innovate. A big thank you to the entire Botika team and partners for contributing to this incredible achievement. Let’s move forward towards a brighter, more innovative future!
+- 2021 (Asean ICT)
+Awards/Achievement: Bronze Winner 2021
+Products: Omnibotika
+Descriptions: Bronze Winner 2021. AICTA is an event that recognizes the best ICT works across the ASEAN region, serving as a benchmark for success in terms of innovation and creativity. AICTA offers business opportunities and promotes trade relations, thereby strengthening the technology and informatics sector in ASEAN and internationally. It also serves as a platform to promote the ICT achievements of ASEAN countries on a global scale.
+- 2020 (SXSW (Austin-Texas))
+Awards/Achievement: As Indonesian Representative 2020
+Products: Omnibotika &amp; Chatbotika
+Descriptions: We are proud to have been published in the AI Journal for our innovative use of AI in customer support. Our cutting-edge technology is transforming the way businesses interact with their customers, providing efficient and personalized solutions.
+- 2018 (Telkomsel NextDev)
+Awards/Achievement: 2nd Evangelist 2018
+Products: Omnibotika &amp; Chatbotika
+Descriptions: We are proud to have been published in the AI Journal for our innovative use of AI in customer support. Our cutting-edge technology is transforming the way businesses interact with their customers, providing efficient and personalized solutions.</t>
+  </si>
+  <si>
+    <t>Bagaimana prosedur jika ada perubahan flow di masa depan?</t>
+  </si>
+  <si>
+    <t>Penghargaan apa aja yang pernah diraih Botika?</t>
+  </si>
+  <si>
+    <t>Jika ada perubahan flow bisa melakukan email ke IT analyst atau ke team support kami.</t>
+  </si>
+  <si>
+    <t>Untuk menagih hutang sebaiknya menggunakan produk Botika yang mana?</t>
+  </si>
+  <si>
+    <t>Gimana kalau ada perubahan flow chatbot?</t>
+  </si>
+  <si>
+    <t>Untuk menagih utang, Blastika adalah pilihan yang tepat. Aplikasi ini dirancang khusus untuk melakukan panggilan massal secara otomatis, sehingga sangat efisien untuk menjangkau banyak orang dalam waktu singkat. Dengan Blastika, Anda dapat menyampaikan pesan atau pengingat pembayaran kepada banyak penerima sekaligus, memastikan pesan Anda tersampaikan tanpa harus melakukan panggilan satu per satu. Selain itu, penggunaan Blastika dapat menghemat waktu dan tenaga, serta meningkatkan efektivitas komunikasi bisnis Anda</t>
+  </si>
+  <si>
+    <t>Berapa jumlah flow yang diberikan saat implementasi awal?</t>
+  </si>
+  <si>
+    <t>Produk Botika mana yang cocok buat nagih hutang?</t>
+  </si>
+  <si>
+    <t>Untuk jumlah flow yang diberikan saat implementasi awal ini bergantung pada kesepakatan pada saat pembuatan SOW</t>
+  </si>
+  <si>
+    <t>Apakah LLM bisa digunakan untuk membantu menulis artikel atau laporan?</t>
+  </si>
+  <si>
+    <t>Flow awal implementasi ada berapa?</t>
+  </si>
+  <si>
+    <t>Silakan hubungi tim support kami melalui email di support@botika.online. Kami akan dengan segera memberikan solusi terbaik untuk kebutuhan Anda. Terima kasih atas kepercayaan Anda kepada layanan kami, dan kami menantikan kesempatan untuk membantu Anda lebih lanjut.</t>
+  </si>
+  <si>
+    <t>Competitive Advantage
+Kelebihan/Keunggulan Produk Botika</t>
+  </si>
+  <si>
+    <t>Bisa nggak LLM nulis artikel buat gue?</t>
+  </si>
+  <si>
+    <t>Berikut kelebihan atau keunggulan dari produk Botika:
+- Kombinasi Chatbot dan Omni Channel
+Kolaborasi manusia dengan mesin. Chatbot dapat mengeskalasi kasus kepada agen untuk sentuhan manusia dan penyelesaian masalah yang kompleks.
+- Teknologi Suara Internal
+Speech To Text dan Text To Voice untuk memungkinkan komunikasi berbasis suara untuk speaker pintar dan telepon.
+- Terhubung dengan Sistem yang Ada Melalui API dengan Mulus
+Menghubungkan sistem yang ada ke chatbot untuk bertransaksi dengan pelanggan dan mendapatkan data yang relevan.
+- Sangat Dapat Disesuaikan
+Dengan mudah membuat persona chatbot dan karakter suara yang sesuai dengan merek dan target pasar.
+- Pengiriman Cepat
+Waktu rata-rata untuk pengembangan khusus hingga rilis versi kurang dari 4 minggu.
+- Harga Kompetitif, Layanan Unggul
+NLP dan Pembelajaran Mesin Internal dalam Bahasa Lokal Mesin internal yang dibangun untuk memastikan inovasi cepat dan fleksibilitas dalam melayani pelanggan dalam bahasa mereka.</t>
+  </si>
+  <si>
+    <t>Penawaran KiosK atau Layanan ke Botika</t>
+  </si>
+  <si>
+    <t>Apa aja sih kelebihan Botika?</t>
+  </si>
+  <si>
+    <t>Terkait penawaran ke Botika terkait KiosK atau layanan lainnya, silakan hubungi kami melalui email berikut: To: galuh@botika.online</t>
+  </si>
+  <si>
+    <t>Batasan Karakter untuk Persona</t>
+  </si>
+  <si>
+    <t>Mau penawaran kios atau layanan ke Botika, hubungi siapa?</t>
+  </si>
+  <si>
+    <t>Saat ini, belum ada batasan maksimal karakter yang ditetapkan untuk persona chatbot. Anda dapat memasukkan deskripsi persona sesuai kebutuhan tanpa khawatir tentang batasan karakter. Ini memberikan fleksibilitas dalam mendefinisikan kepribadian dan karakter chatbot Anda dengan lebih detail dan sesuai dengan tujuan penggunaan.</t>
+  </si>
+  <si>
+    <t>Unique user artinya apa ?</t>
+  </si>
+  <si>
+    <t>Ada batasan karakter buat persona chatbot nggak?</t>
+  </si>
+  <si>
+    <t>User yang sudah melakukan chat dalam kurun waktu tertentu biasanya per bulan</t>
+  </si>
+  <si>
+    <t>Permintaan Penambahan Kontrak Total License</t>
+  </si>
+  <si>
+    <t>Unique user itu maksudnya apa sih?</t>
+  </si>
+  <si>
+    <t>Untuk penambahan license agent omnibotika, dapat mengirimkan email ke:
+To: galuh@botika.online</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +469,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -127,13 +485,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9CB9C"/>
+        <fgColor rgb="FFF4CCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
+        <fgColor rgb="FFFFE599"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -173,7 +531,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -190,10 +548,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -202,14 +557,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -527,238 +882,388 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="105" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D2" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:4" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="286.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="247.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="B14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="144" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="53" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="196" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="40" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="B31" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3"/>
@@ -1181,10 +1686,10 @@
       <c r="D101" s="4"/>
     </row>
     <row r="102" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="7"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
     </row>
     <row r="103" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="2"/>

--- a/assets/xlsx/testing.xlsx
+++ b/assets/xlsx/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMG\Documents\GITHUB\automationtestingjudges\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279DFE6E-02F6-4810-9925-9CD1A5FFCF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807B54F4-4815-47C8-920B-25979DEB51CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -923,7 +923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -966,7 +966,9 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
       <c r="B7" s="9" t="s">
         <v>19</v>
       </c>
@@ -978,7 +980,9 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3"/>
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
       <c r="B8" s="9" t="s">
         <v>22</v>
       </c>
@@ -990,7 +994,9 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3"/>
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
       <c r="B9" s="9" t="s">
         <v>25</v>
       </c>
@@ -1002,7 +1008,9 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
       <c r="B10" s="9" t="s">
         <v>28</v>
       </c>
@@ -1014,7 +1022,9 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2"/>
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
       <c r="B11" s="9" t="s">
         <v>31</v>
       </c>
@@ -1026,7 +1036,9 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="286.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3"/>
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
       <c r="B12" s="9" t="s">
         <v>34</v>
       </c>
@@ -1038,7 +1050,9 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="247.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3"/>
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
       <c r="B13" s="9" t="s">
         <v>37</v>
       </c>
@@ -1050,7 +1064,9 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
       <c r="B14" s="9" t="s">
         <v>40</v>
       </c>
@@ -1061,8 +1077,10 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
       <c r="B15" s="11" t="s">
         <v>43</v>
       </c>
@@ -1074,7 +1092,9 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3"/>
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
       <c r="B16" s="11" t="s">
         <v>46</v>
       </c>
@@ -1086,7 +1106,9 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="144" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3"/>
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
       <c r="B17" s="9" t="s">
         <v>48</v>
       </c>
@@ -1098,7 +1120,9 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
       <c r="B18" s="9" t="s">
         <v>51</v>
       </c>
@@ -1110,7 +1134,9 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3"/>
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
       <c r="B19" s="9" t="s">
         <v>54</v>
       </c>
@@ -1122,7 +1148,9 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3"/>
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
       <c r="B20" s="9" t="s">
         <v>57</v>
       </c>
@@ -1134,7 +1162,9 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3"/>
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
       <c r="B21" s="9" t="s">
         <v>60</v>
       </c>
@@ -1146,7 +1176,9 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3"/>
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
       <c r="B22" s="9" t="s">
         <v>63</v>
       </c>
@@ -1158,7 +1190,9 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="3"/>
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
       <c r="B23" s="9" t="s">
         <v>66</v>
       </c>
@@ -1170,7 +1204,9 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="53" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="2"/>
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
       <c r="B24" s="9" t="s">
         <v>69</v>
       </c>
@@ -1182,7 +1218,9 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
       <c r="B25" s="9" t="s">
         <v>72</v>
       </c>
@@ -1194,7 +1232,9 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="3"/>
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
       <c r="B26" s="9" t="s">
         <v>75</v>
       </c>
@@ -1206,7 +1246,9 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="196" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="3"/>
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
       <c r="B27" s="9" t="s">
         <v>78</v>
       </c>
@@ -1218,7 +1260,9 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="2"/>
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
       <c r="B28" s="9" t="s">
         <v>81</v>
       </c>
@@ -1230,7 +1274,9 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="40" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="2"/>
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
       <c r="B29" s="9" t="s">
         <v>84</v>
       </c>
@@ -1242,7 +1288,9 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="2"/>
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
       <c r="B30" s="9" t="s">
         <v>87</v>
       </c>
@@ -1254,7 +1302,9 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="2"/>
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
       <c r="B31" s="9" t="s">
         <v>90</v>
       </c>

--- a/assets/xlsx/testing.xlsx
+++ b/assets/xlsx/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMG\Documents\GITHUB\automationtestingjudges\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807B54F4-4815-47C8-920B-25979DEB51CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB40EADB-2198-4CD6-99C7-C4FD7EAB9F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>No</t>
   </si>
@@ -34,65 +34,6 @@
     <t>Context</t>
   </si>
   <si>
-    <t>Lokasi Kantor Botika</t>
-  </si>
-  <si>
-    <t>Kantor Botika ada di mana sih?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEAD OFFICE
-Jl Perumnas Blok E III No 50
-Seturan Yogyakarta
-TECHNICAL OFFICE
-Yunion Space, Agres ID Lt 3,
-Jl. C. Simanjuntak No.101, Terban, Kec. Gondokusuman, Kota Yogyakarta, Daerah Istimewa Yogyakarta 55223
-</t>
-  </si>
-  <si>
-    <t>Jam Layanan Botika</t>
-  </si>
-  <si>
-    <t>Botika buka kapan aja?</t>
-  </si>
-  <si>
-    <t>Opening Hour
-Monday – Friday: 8.30 WIB – 17.00 WIB
-Saturday – Sunday: Libur</t>
-  </si>
-  <si>
-    <t>Kontak Botika</t>
-  </si>
-  <si>
-    <t>Gimana cara menghubungi Botika?</t>
-  </si>
-  <si>
-    <t>Email
-support@botika.online
-Call Service
-+6288978001099 (Call Only)
-+6281802207000 (Whatsapp Only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Siapa Botika?
-Botika Itu Apa</t>
-  </si>
-  <si>
-    <t>Botika itu apa sih?</t>
-  </si>
-  <si>
-    <t>Perusahan dengan teknologi kecerdasan buatan yang mampu melakukan pembelajaran mesin (machine learning) dan pemrosesan bahasa alamiah (natural language processing (NLP)) atas bahasa lokal, sehingga memudahkan para pelaku bisnis untuk melayani sejumlah besar pelanggan dan mengurangi biaya, namun di saat yang sama meningkatkan kualitas pelayanan.</t>
-  </si>
-  <si>
-    <t>Teknologi Kami</t>
-  </si>
-  <si>
-    <t>Teknologi apa yang dipakai Botika?</t>
-  </si>
-  <si>
-    <t>Botika menawarkan chatbot berbasis AI dan omnichannel dashboard yang memudahkan pelaku bisnis menangani konsumen. Teknologi kami mengerti apa kebutuhan Anda dan memiliki kemampuan otomotis untuk: melakukan pekerjaan-pekerjaan repetitif, melakukan percakapan, bertransaksi dan bercakap-cakap secara intelektual baik dengan pelanggan dalam bentuk teks atau suara dalam berbagai media seperti e-mail, Whatsapp, LINE, Messenger, Telegram, website, aplikasi mobile, dan lain-lain.</t>
-  </si>
-  <si>
     <t>Untuk menjalin kerjasama dan kesempatan investasi
 (Bagaimana cara menjalin kerjasama dan menemukan kesmepatan investasi?)</t>
   </si>
@@ -102,142 +43,6 @@
   <si>
     <t>hubungi kami melalui admin@botika.online
 (Untuk menjalin kerjasama atau mengeksplorasi peluang investasi, silakan hubungi kami di admin@botika.online.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tertarik dengan AI/Machine Learning?
-</t>
-  </si>
-  <si>
-    <t>Pengen kerja di tim AI/Machine Learning Botika?</t>
-  </si>
-  <si>
-    <t>Bergabunglah dengan tim kami yang terus berkembang 🚀
-Kami membuka kesempatan untuk bergabung melalui:
-• Program Magang
-• Lowongan Kerja 
-Silakan kirimkan CV dan dokumen pendukung Anda ke:
-📧 hrd@botika.online
-Gunakan subject email:
-[Magang / Posisi yang Dilamar] – [Nama Lengkap]
-Kami menantikan talenta terbaik untuk berkembang bersama kami di industri Artificial Intelligence.</t>
-  </si>
-  <si>
-    <t>Visi misi</t>
-  </si>
-  <si>
-    <t>Apa visi dan misi Botika?</t>
-  </si>
-  <si>
-    <t>Misi
-Menyediakan asisten AI yang bisa berinteraksi baik dalam teks maupun suara menggunakan channel komunikasi moderen
-Visi
-Kecerdasan buartan untuk melayani kebutuhan manusia</t>
-  </si>
-  <si>
-    <t>Pasar internasional yang menggunakan layanan Botika</t>
-  </si>
-  <si>
-    <t>Botika udah dipakai di negara mana aja?</t>
-  </si>
-  <si>
-    <t>Indonesia, Malaysia, Singapore, Philippines, Thailand, Bangladesh, Vietnam, Cambodia, South Korea, Japan, Taiwan, South China, North and East China.</t>
-  </si>
-  <si>
-    <t>Road Map Botika</t>
-  </si>
-  <si>
-    <t>Gimana roadmap perkembangan Botika?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017
-Chatbot
-Text based conversational AI for social media : whatsapp, facebook, instagram, twitter, line, telegram, livechat, email
-2018
-Omnibotika
-is a all in one dashboard to help customer services in serving consumers to achieve target and help you to satisfy your consumers.
-2018
-Text to Speech
-Text to speech and speech to text, creating voice with natural neural network technology.
-2018
-Speech to Text
-can be integrated with artificial intelligence, so that it can simplify our daily activities.
-2019
-Voice Botika
-For creating Chatbot &amp; Voicebot using Botika engine
-2019
-Smart Speaker
-can be integrated with artificial intelligence, so that it can simplify our daily activities
-2020
-Platform
-An all-in-one platform to build and launch conversational chatbots without coding.
-2021
-VB App
-VB is an application with the “Luna” bot and Indonesian text to speech technology with two voice options
-2022
-Wabis Botika
-is a platform to upgrade you whatsapp business to whatsapp business API with masking name and green thick
-</t>
-  </si>
-  <si>
-    <t>Botika teknologi</t>
-  </si>
-  <si>
-    <t>Teknologi apa aja yang ada di Botika?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEXT
-POS Tagging
-Sentence Boundaries
-Text Chunking
-Syntax Analysis
-Language Modeling
-Question Answering
-Intent Classification
-Named Entity Recognition (NER)
-Topic Detection
-Text Summarization
-Text Generation
-Word Tokenization
-TEXT &amp; VOICE 
-Speech Recognition(STT) 
-Speech Synthesizing (TTS) 
-COMPUTER VISION
-OCR 
-Image Classification 
-Face Recognition 
-</t>
-  </si>
-  <si>
-    <t>Competitive Advantage</t>
-  </si>
-  <si>
-    <t>Apa keunggulan Botika dibanding yang lain?</t>
-  </si>
-  <si>
-    <t>Kombinasi Chatbot dan Omni Channel
-Kolaborasi manusia dengan mesin. Chatbot dapat mengeskalasi kasus kepada agen untuk sentuhan manusia dan penyelesaian masalah yang kompleks.
-Teknologi Suara Internal
-Speech To Text dan Text To Voice untuk memungkinkan komunikasi berbasis suara untuk speaker pintar dan telepon.
-Terhubung dengan Sistem yang Ada Melalui API dengan Mulus
-Menghubungkan sistem yang ada ke chatbot untuk bertransaksi dengan pelanggan dan mendapatkan data yang relevan.
-Sangat Dapat Disesuaikan
-Dengan mudah membuat persona chatbot dan karakter suara yang sesuai dengan merek dan target pasar.
-Pengiriman Cepat
-Waktu rata-rata untuk pengembangan khusus hingga rilis versi kurang dari 4 minggu.
-Harga Kompetitif, Layanan Unggul
-NLP dan Pembelajaran Mesin Internal dalam Bahasa Lokal Mesin internal yang dibangun untuk memastikan inovasi cepat dan fleksibilitas dalam melayani pelanggan dalam bahasa mereka.</t>
-  </si>
-  <si>
-    <t>Team Member</t>
-  </si>
-  <si>
-    <t>Siapa aja tim di balik Botika?</t>
-  </si>
-  <si>
-    <t>Ide BOTIKA dimulai pada tanggal 1 September 2016 oleh dua pemuda dari Yogyakarta, Dito Anindita dan Galuh Koco Sadewo.
-Untuk mewujudkan ide ini, mereka juga berkolaborasi dengan Prima Kharisma, Eri Kuncoro, dan Vita Subiyakti untuk membuat terobosan dalam teknologi AI di Indonesia.
-Dengan ini, mereka percaya bahwa teknologi AI mampu menyederhanakan setiap aspek kehidupan manusia.
-Sekarang Botika sudah memiliki 50 karyawan yang tersebar di Yogyakarta dan Jakarta</t>
   </si>
   <si>
     <t>Informasi magang/pkl</t>
@@ -253,182 +58,6 @@
   </si>
   <si>
     <t>Ada lowongan kerja nggak di Botika?</t>
-  </si>
-  <si>
-    <t>Untuk menjalin kerjasama dan kesempatan investasi</t>
-  </si>
-  <si>
-    <t>Mau tawarin kios atau layanan ke Botika, gimana caranya?</t>
-  </si>
-  <si>
-    <t>Produk Business and Partnership di Botika berfokus pada pembangunan kerja sama strategis dengan berbagai pihak untuk memperluas peluang bisnis dan menciptakan nilai bersama.
-Melalui program ini, Botika membuka kesempatan bagi perusahaan, lembaga, maupun individu untuk menjalin kemitraan bisnis, kolaborasi teknologi, atau kerja sama komersial yang saling menguntungkan.
-Setiap bentuk kerja sama akan disesuaikan dengan kebutuhan dan tujuan masing-masing mitra, dengan fokus pada pengembangan bisnis, inovasi produk, dan peningkatan efisiensi operasional.
-Jika Anda tertarik menjalin kerja sama atau ingin mengeksplorasi peluang kemitraan dan investasi, silakan hubungi kami melalui email di galuh@botika.online</t>
-  </si>
-  <si>
-    <t>Apa saja produk di Botika?</t>
-  </si>
-  <si>
-    <t>Mau proposal kerjasama, emailnya ke mana?</t>
-  </si>
-  <si>
-    <t>Produk produk di botika antara lain, LLM, Digital Human AI (Virtual Avatar), Omnibotika, Voicebotika, Blastika, Chatbotika, Platform, Wabis (Whatsapp Business). Untuk penjelasan produk lebih lanjut silakan kunjungi https://botika.online/product</t>
-  </si>
-  <si>
-    <t>Portofolio Botika</t>
-  </si>
-  <si>
-    <t>Produk apa aja sih yang ada di Botika?</t>
-  </si>
-  <si>
-    <t>Untuk melihat portofolio Botika, silakan kunjungi https://botika.online/. Di sana, terdapat penjelasan singkat mengenai produk-produk kami dan berbagai use case dari tiap klien yang telah menggunakan layanan Botika.</t>
-  </si>
-  <si>
-    <t>berapa SLA yang diperlukan, khususnya untuk perubahan mendadak (misalnya, d</t>
-  </si>
-  <si>
-    <t>Portofolio Botika bisa dilihat di mana?</t>
-  </si>
-  <si>
-    <t>Untuk perubahan ini nanti akan berbeda-beda untuk timelinenya bergantung dengan seberapa banyak yang perlu diubah dan apakah masuk ke Mayor, Medium, Minor. Untuk lebih jelasnya dapat mengikuti panduan SLA dibawha ini ;</t>
-  </si>
-  <si>
-    <t>Siapa kamu?
-Kamu itu siapa?
-Perkenalkan dirimu
-Luna siapanya botika</t>
-  </si>
-  <si>
-    <t>SLA-nya gimana tuh kalau ada perubahan?</t>
-  </si>
-  <si>
-    <t>Perkenalkan, saya Luna, asisten virtual dari Botika. Saya siap membantu menjawab pertanyaan seputar produk Botika, mengatasi kendala yang Anda alami, serta menjawab pertanyaan umum lainnya. Jangan ragu untuk bertanya, saya selalu tersedia untuk Anda.</t>
-  </si>
-  <si>
-    <t>Penghargaan Botika
-Pencapaian terbesar Botika</t>
-  </si>
-  <si>
-    <t>Kamu ini siapa sih?</t>
-  </si>
-  <si>
-    <t>Berikut pencapaian terbesar yang telah diraih dan penghargaan industri yang diterima Botika atas solusi AI-nya yang inovatif:
-- 2024 (Microsoft BUILD: AI Day)
-Awards/Achievement: KAI partner for digital human AI
-Products: Superchatbot &amp; Digital Human AI botika: Nilam KAI
-Descriptions: Microsoft Chairman and CEO, Satya Nadella, visited Indonesia to meet with Microsoft partners utilizing AI technology in everyday applications. As part of this visit, Botika was highlighted for its collaboration with Microsoft in developing a digital human AI for KAI, demonstrating the innovative integration of AI into real-world solutions.
-- 2023 (Microsoft Generative AI Champion 2023)
-Awards/Achievement: Microsoft Indonesia Partner Award
-Products: Superchatbot &amp; Digital Human AI Botika
-Descriptions: Reaching New Heights with Generative AI! We are proud to announce that Botika has been named a Generative AI Champion Partner at the FY 24 Microsoft Indonesia Kick Off event, themed 'Empowering Growth and Innovation in Indonesia.' The event, held at Glass House, Ritz Carlton Pacific Place, Jakarta, reaffirms our commitment to driving growth and innovation in the country.The award was presented by Microsoft Indonesia President Director, Darma Simorangkir, to Galuh Koco Sadewo, Co-Founder &amp; CBD of Botika Teknologi. We believe Generative AI will revolutionize the business and communication landscape, and together with Microsoft, we will continue delivering advanced solutions to help Indonesian businesses grow and innovate. A big thank you to the entire Botika team and partners for contributing to this incredible achievement. Let’s move forward towards a brighter, more innovative future!
-- 2021 (Asean ICT)
-Awards/Achievement: Bronze Winner 2021
-Products: Omnibotika
-Descriptions: Bronze Winner 2021. AICTA is an event that recognizes the best ICT works across the ASEAN region, serving as a benchmark for success in terms of innovation and creativity. AICTA offers business opportunities and promotes trade relations, thereby strengthening the technology and informatics sector in ASEAN and internationally. It also serves as a platform to promote the ICT achievements of ASEAN countries on a global scale.
-- 2020 (SXSW (Austin-Texas))
-Awards/Achievement: As Indonesian Representative 2020
-Products: Omnibotika &amp; Chatbotika
-Descriptions: We are proud to have been published in the AI Journal for our innovative use of AI in customer support. Our cutting-edge technology is transforming the way businesses interact with their customers, providing efficient and personalized solutions.
-- 2018 (Telkomsel NextDev)
-Awards/Achievement: 2nd Evangelist 2018
-Products: Omnibotika &amp; Chatbotika
-Descriptions: We are proud to have been published in the AI Journal for our innovative use of AI in customer support. Our cutting-edge technology is transforming the way businesses interact with their customers, providing efficient and personalized solutions.</t>
-  </si>
-  <si>
-    <t>Bagaimana prosedur jika ada perubahan flow di masa depan?</t>
-  </si>
-  <si>
-    <t>Penghargaan apa aja yang pernah diraih Botika?</t>
-  </si>
-  <si>
-    <t>Jika ada perubahan flow bisa melakukan email ke IT analyst atau ke team support kami.</t>
-  </si>
-  <si>
-    <t>Untuk menagih hutang sebaiknya menggunakan produk Botika yang mana?</t>
-  </si>
-  <si>
-    <t>Gimana kalau ada perubahan flow chatbot?</t>
-  </si>
-  <si>
-    <t>Untuk menagih utang, Blastika adalah pilihan yang tepat. Aplikasi ini dirancang khusus untuk melakukan panggilan massal secara otomatis, sehingga sangat efisien untuk menjangkau banyak orang dalam waktu singkat. Dengan Blastika, Anda dapat menyampaikan pesan atau pengingat pembayaran kepada banyak penerima sekaligus, memastikan pesan Anda tersampaikan tanpa harus melakukan panggilan satu per satu. Selain itu, penggunaan Blastika dapat menghemat waktu dan tenaga, serta meningkatkan efektivitas komunikasi bisnis Anda</t>
-  </si>
-  <si>
-    <t>Berapa jumlah flow yang diberikan saat implementasi awal?</t>
-  </si>
-  <si>
-    <t>Produk Botika mana yang cocok buat nagih hutang?</t>
-  </si>
-  <si>
-    <t>Untuk jumlah flow yang diberikan saat implementasi awal ini bergantung pada kesepakatan pada saat pembuatan SOW</t>
-  </si>
-  <si>
-    <t>Apakah LLM bisa digunakan untuk membantu menulis artikel atau laporan?</t>
-  </si>
-  <si>
-    <t>Flow awal implementasi ada berapa?</t>
-  </si>
-  <si>
-    <t>Silakan hubungi tim support kami melalui email di support@botika.online. Kami akan dengan segera memberikan solusi terbaik untuk kebutuhan Anda. Terima kasih atas kepercayaan Anda kepada layanan kami, dan kami menantikan kesempatan untuk membantu Anda lebih lanjut.</t>
-  </si>
-  <si>
-    <t>Competitive Advantage
-Kelebihan/Keunggulan Produk Botika</t>
-  </si>
-  <si>
-    <t>Bisa nggak LLM nulis artikel buat gue?</t>
-  </si>
-  <si>
-    <t>Berikut kelebihan atau keunggulan dari produk Botika:
-- Kombinasi Chatbot dan Omni Channel
-Kolaborasi manusia dengan mesin. Chatbot dapat mengeskalasi kasus kepada agen untuk sentuhan manusia dan penyelesaian masalah yang kompleks.
-- Teknologi Suara Internal
-Speech To Text dan Text To Voice untuk memungkinkan komunikasi berbasis suara untuk speaker pintar dan telepon.
-- Terhubung dengan Sistem yang Ada Melalui API dengan Mulus
-Menghubungkan sistem yang ada ke chatbot untuk bertransaksi dengan pelanggan dan mendapatkan data yang relevan.
-- Sangat Dapat Disesuaikan
-Dengan mudah membuat persona chatbot dan karakter suara yang sesuai dengan merek dan target pasar.
-- Pengiriman Cepat
-Waktu rata-rata untuk pengembangan khusus hingga rilis versi kurang dari 4 minggu.
-- Harga Kompetitif, Layanan Unggul
-NLP dan Pembelajaran Mesin Internal dalam Bahasa Lokal Mesin internal yang dibangun untuk memastikan inovasi cepat dan fleksibilitas dalam melayani pelanggan dalam bahasa mereka.</t>
-  </si>
-  <si>
-    <t>Penawaran KiosK atau Layanan ke Botika</t>
-  </si>
-  <si>
-    <t>Apa aja sih kelebihan Botika?</t>
-  </si>
-  <si>
-    <t>Terkait penawaran ke Botika terkait KiosK atau layanan lainnya, silakan hubungi kami melalui email berikut: To: galuh@botika.online</t>
-  </si>
-  <si>
-    <t>Batasan Karakter untuk Persona</t>
-  </si>
-  <si>
-    <t>Mau penawaran kios atau layanan ke Botika, hubungi siapa?</t>
-  </si>
-  <si>
-    <t>Saat ini, belum ada batasan maksimal karakter yang ditetapkan untuk persona chatbot. Anda dapat memasukkan deskripsi persona sesuai kebutuhan tanpa khawatir tentang batasan karakter. Ini memberikan fleksibilitas dalam mendefinisikan kepribadian dan karakter chatbot Anda dengan lebih detail dan sesuai dengan tujuan penggunaan.</t>
-  </si>
-  <si>
-    <t>Unique user artinya apa ?</t>
-  </si>
-  <si>
-    <t>Ada batasan karakter buat persona chatbot nggak?</t>
-  </si>
-  <si>
-    <t>User yang sudah melakukan chat dalam kurun waktu tertentu biasanya per bulan</t>
-  </si>
-  <si>
-    <t>Permintaan Penambahan Kontrak Total License</t>
-  </si>
-  <si>
-    <t>Unique user itu maksudnya apa sih?</t>
-  </si>
-  <si>
-    <t>Untuk penambahan license agent omnibotika, dapat mengirimkan email ke:
-To: galuh@botika.online</t>
   </si>
 </sst>
 </file>
@@ -531,7 +160,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -559,9 +188,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -872,7 +498,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D1000"/>
+  <dimension ref="A1:D973"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
@@ -895,7 +521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="105" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -905,427 +531,211 @@
       <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3">
+      <c r="D4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="286.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="247.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3">
-        <v>15</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="144" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3">
-        <v>20</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3">
-        <v>21</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="3">
-        <v>22</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="53" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="3">
-        <v>23</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="3">
-        <v>24</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="3">
-        <v>25</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="196" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="3">
-        <v>26</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="3">
-        <v>27</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="40" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="3">
-        <v>28</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="3">
-        <v>29</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="3"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2"/>
@@ -1339,35 +749,35 @@
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="3"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="3"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-    </row>
-    <row r="39" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="3"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
+    <row r="36" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="3"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3"/>
@@ -1381,29 +791,29 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="3"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-    </row>
-    <row r="46" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+    <row r="43" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="3"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="3"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
     </row>
     <row r="47" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3"/>
@@ -1429,11 +839,11 @@
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
     </row>
-    <row r="51" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+    <row r="51" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="3"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
     </row>
     <row r="52" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3"/>
@@ -1477,29 +887,29 @@
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
     </row>
-    <row r="59" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-    </row>
-    <row r="60" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-    </row>
-    <row r="61" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-    </row>
-    <row r="62" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+    <row r="59" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="3"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
     </row>
     <row r="63" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2"/>
@@ -1507,11 +917,11 @@
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+    <row r="64" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
     </row>
     <row r="65" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2"/>
@@ -1531,17 +941,17 @@
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
     </row>
-    <row r="68" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="3"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-    </row>
-    <row r="69" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+    <row r="68" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
     </row>
     <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="3"/>
@@ -1565,7 +975,7 @@
       <c r="A73" s="3"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
+      <c r="D73" s="5"/>
     </row>
     <row r="74" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3"/>
@@ -1573,179 +983,179 @@
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
     </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="3"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="3"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
+    <row r="75" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+    </row>
+    <row r="76" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
     </row>
     <row r="77" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="3"/>
+      <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
     </row>
     <row r="78" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="3"/>
+      <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
     </row>
     <row r="79" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="3"/>
+      <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
     </row>
     <row r="80" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="3"/>
+      <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
     </row>
     <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="3"/>
+      <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
     </row>
-    <row r="82" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
+    <row r="82" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
     </row>
     <row r="83" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="3"/>
+      <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
     </row>
     <row r="84" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="3"/>
+      <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
     </row>
     <row r="85" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="3"/>
+      <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
     </row>
     <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="3"/>
+      <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
     </row>
     <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="3"/>
+      <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
     </row>
     <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="3"/>
+      <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
     </row>
     <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="3"/>
+      <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
     </row>
-    <row r="90" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
+    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
     </row>
     <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="3"/>
+      <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
     </row>
-    <row r="92" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
+    <row r="92" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
     </row>
     <row r="93" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="3"/>
+      <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
     </row>
-    <row r="94" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-    </row>
-    <row r="95" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
+    <row r="94" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+    </row>
+    <row r="95" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
     </row>
     <row r="96" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="3"/>
+      <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
     </row>
     <row r="97" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="3"/>
+      <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
     </row>
-    <row r="98" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
+    <row r="98" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
     </row>
     <row r="99" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="3"/>
+      <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
     </row>
     <row r="100" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="3"/>
+      <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
-      <c r="D100" s="5"/>
+      <c r="D100" s="4"/>
     </row>
     <row r="101" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="3"/>
+      <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
     </row>
-    <row r="102" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-    </row>
-    <row r="103" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
+    <row r="102" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+    </row>
+    <row r="103" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
     </row>
     <row r="104" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="4"/>
@@ -6967,168 +6377,6 @@
       <c r="C973" s="4"/>
       <c r="D973" s="4"/>
     </row>
-    <row r="974" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A974" s="4"/>
-      <c r="B974" s="4"/>
-      <c r="C974" s="4"/>
-      <c r="D974" s="4"/>
-    </row>
-    <row r="975" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A975" s="4"/>
-      <c r="B975" s="4"/>
-      <c r="C975" s="4"/>
-      <c r="D975" s="4"/>
-    </row>
-    <row r="976" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A976" s="4"/>
-      <c r="B976" s="4"/>
-      <c r="C976" s="4"/>
-      <c r="D976" s="4"/>
-    </row>
-    <row r="977" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A977" s="4"/>
-      <c r="B977" s="4"/>
-      <c r="C977" s="4"/>
-      <c r="D977" s="4"/>
-    </row>
-    <row r="978" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A978" s="4"/>
-      <c r="B978" s="4"/>
-      <c r="C978" s="4"/>
-      <c r="D978" s="4"/>
-    </row>
-    <row r="979" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A979" s="4"/>
-      <c r="B979" s="4"/>
-      <c r="C979" s="4"/>
-      <c r="D979" s="4"/>
-    </row>
-    <row r="980" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A980" s="4"/>
-      <c r="B980" s="4"/>
-      <c r="C980" s="4"/>
-      <c r="D980" s="4"/>
-    </row>
-    <row r="981" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A981" s="4"/>
-      <c r="B981" s="4"/>
-      <c r="C981" s="4"/>
-      <c r="D981" s="4"/>
-    </row>
-    <row r="982" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A982" s="4"/>
-      <c r="B982" s="4"/>
-      <c r="C982" s="4"/>
-      <c r="D982" s="4"/>
-    </row>
-    <row r="983" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A983" s="4"/>
-      <c r="B983" s="4"/>
-      <c r="C983" s="4"/>
-      <c r="D983" s="4"/>
-    </row>
-    <row r="984" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A984" s="4"/>
-      <c r="B984" s="4"/>
-      <c r="C984" s="4"/>
-      <c r="D984" s="4"/>
-    </row>
-    <row r="985" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A985" s="4"/>
-      <c r="B985" s="4"/>
-      <c r="C985" s="4"/>
-      <c r="D985" s="4"/>
-    </row>
-    <row r="986" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A986" s="4"/>
-      <c r="B986" s="4"/>
-      <c r="C986" s="4"/>
-      <c r="D986" s="4"/>
-    </row>
-    <row r="987" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A987" s="4"/>
-      <c r="B987" s="4"/>
-      <c r="C987" s="4"/>
-      <c r="D987" s="4"/>
-    </row>
-    <row r="988" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A988" s="4"/>
-      <c r="B988" s="4"/>
-      <c r="C988" s="4"/>
-      <c r="D988" s="4"/>
-    </row>
-    <row r="989" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A989" s="4"/>
-      <c r="B989" s="4"/>
-      <c r="C989" s="4"/>
-      <c r="D989" s="4"/>
-    </row>
-    <row r="990" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A990" s="4"/>
-      <c r="B990" s="4"/>
-      <c r="C990" s="4"/>
-      <c r="D990" s="4"/>
-    </row>
-    <row r="991" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A991" s="4"/>
-      <c r="B991" s="4"/>
-      <c r="C991" s="4"/>
-      <c r="D991" s="4"/>
-    </row>
-    <row r="992" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A992" s="4"/>
-      <c r="B992" s="4"/>
-      <c r="C992" s="4"/>
-      <c r="D992" s="4"/>
-    </row>
-    <row r="993" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A993" s="4"/>
-      <c r="B993" s="4"/>
-      <c r="C993" s="4"/>
-      <c r="D993" s="4"/>
-    </row>
-    <row r="994" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A994" s="4"/>
-      <c r="B994" s="4"/>
-      <c r="C994" s="4"/>
-      <c r="D994" s="4"/>
-    </row>
-    <row r="995" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A995" s="4"/>
-      <c r="B995" s="4"/>
-      <c r="C995" s="4"/>
-      <c r="D995" s="4"/>
-    </row>
-    <row r="996" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A996" s="4"/>
-      <c r="B996" s="4"/>
-      <c r="C996" s="4"/>
-      <c r="D996" s="4"/>
-    </row>
-    <row r="997" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A997" s="4"/>
-      <c r="B997" s="4"/>
-      <c r="C997" s="4"/>
-      <c r="D997" s="4"/>
-    </row>
-    <row r="998" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A998" s="4"/>
-      <c r="B998" s="4"/>
-      <c r="C998" s="4"/>
-      <c r="D998" s="4"/>
-    </row>
-    <row r="999" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A999" s="4"/>
-      <c r="B999" s="4"/>
-      <c r="C999" s="4"/>
-      <c r="D999" s="4"/>
-    </row>
-    <row r="1000" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="4"/>
-      <c r="C1000" s="4"/>
-      <c r="D1000" s="4"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/assets/xlsx/testing.xlsx
+++ b/assets/xlsx/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMG\Documents\GITHUB\automationtestingjudges\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB40EADB-2198-4CD6-99C7-C4FD7EAB9F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC463D6-AB91-4DA9-B60F-06AE67B5774B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="92">
   <si>
     <t>No</t>
   </si>
@@ -58,6 +58,374 @@
   </si>
   <si>
     <t>Ada lowongan kerja nggak di Botika?</t>
+  </si>
+  <si>
+    <t>Lokasi Kantor Botika</t>
+  </si>
+  <si>
+    <t>Kantor Botika ada di mana sih?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAD OFFICE
+Jl Perumnas Blok E III No 50
+Seturan Yogyakarta
+TECHNICAL OFFICE
+Yunion Space, Agres ID Lt 3,
+Jl. C. Simanjuntak No.101, Terban, Kec. Gondokusuman, Kota Yogyakarta, Daerah Istimewa Yogyakarta 55223
+</t>
+  </si>
+  <si>
+    <t>Jam Layanan Botika</t>
+  </si>
+  <si>
+    <t>Botika buka kapan aja?</t>
+  </si>
+  <si>
+    <t>Opening Hour
+Monday – Friday: 8.30 WIB – 17.00 WIB
+Saturday – Sunday: Libur</t>
+  </si>
+  <si>
+    <t>Kontak Botika</t>
+  </si>
+  <si>
+    <t>Gimana cara menghubungi Botika?</t>
+  </si>
+  <si>
+    <t>Email
+support@botika.online
+Call Service
++6288978001099 (Call Only)
++6281802207000 (Whatsapp Only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Siapa Botika?
+Botika Itu Apa</t>
+  </si>
+  <si>
+    <t>Botika itu apa sih?</t>
+  </si>
+  <si>
+    <t>Perusahan dengan teknologi kecerdasan buatan yang mampu melakukan pembelajaran mesin (machine learning) dan pemrosesan bahasa alamiah (natural language processing (NLP)) atas bahasa lokal, sehingga memudahkan para pelaku bisnis untuk melayani sejumlah besar pelanggan dan mengurangi biaya, namun di saat yang sama meningkatkan kualitas pelayanan.</t>
+  </si>
+  <si>
+    <t>Teknologi Kami</t>
+  </si>
+  <si>
+    <t>Teknologi apa yang dipakai Botika?</t>
+  </si>
+  <si>
+    <t>Botika menawarkan chatbot berbasis AI dan omnichannel dashboard yang memudahkan pelaku bisnis menangani konsumen. Teknologi kami mengerti apa kebutuhan Anda dan memiliki kemampuan otomotis untuk: melakukan pekerjaan-pekerjaan repetitif, melakukan percakapan, bertransaksi dan bercakap-cakap secara intelektual baik dengan pelanggan dalam bentuk teks atau suara dalam berbagai media seperti e-mail, Whatsapp, LINE, Messenger, Telegram, website, aplikasi mobile, dan lain-lain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertarik dengan AI/Machine Learning?
+</t>
+  </si>
+  <si>
+    <t>Pengen kerja di tim AI/Machine Learning Botika?</t>
+  </si>
+  <si>
+    <t>Bergabunglah dengan tim kami yang terus berkembang 🚀
+Kami membuka kesempatan untuk bergabung melalui:
+• Program Magang
+• Lowongan Kerja 
+Silakan kirimkan CV dan dokumen pendukung Anda ke:
+📧 hrd@botika.online
+Gunakan subject email:
+[Magang / Posisi yang Dilamar] – [Nama Lengkap]
+Kami menantikan talenta terbaik untuk berkembang bersama kami di industri Artificial Intelligence.</t>
+  </si>
+  <si>
+    <t>Visi misi</t>
+  </si>
+  <si>
+    <t>Apa visi dan misi Botika?</t>
+  </si>
+  <si>
+    <t>Misi
+Menyediakan asisten AI yang bisa berinteraksi baik dalam teks maupun suara menggunakan channel komunikasi moderen
+Visi
+Kecerdasan buartan untuk melayani kebutuhan manusia</t>
+  </si>
+  <si>
+    <t>Pasar internasional yang menggunakan layanan Botika</t>
+  </si>
+  <si>
+    <t>Botika udah dipakai di negara mana aja?</t>
+  </si>
+  <si>
+    <t>Indonesia, Malaysia, Singapore, Philippines, Thailand, Bangladesh, Vietnam, Cambodia, South Korea, Japan, Taiwan, South China, North and East China.</t>
+  </si>
+  <si>
+    <t>Road Map Botika</t>
+  </si>
+  <si>
+    <t>Gimana roadmap perkembangan Botika?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017
+Chatbot
+Text based conversational AI for social media : whatsapp, facebook, instagram, twitter, line, telegram, livechat, email
+2018
+Omnibotika
+is a all in one dashboard to help customer services in serving consumers to achieve target and help you to satisfy your consumers.
+2018
+Text to Speech
+Text to speech and speech to text, creating voice with natural neural network technology.
+2018
+Speech to Text
+can be integrated with artificial intelligence, so that it can simplify our daily activities.
+2019
+Voice Botika
+For creating Chatbot &amp; Voicebot using Botika engine
+2019
+Smart Speaker
+can be integrated with artificial intelligence, so that it can simplify our daily activities
+2020
+Platform
+An all-in-one platform to build and launch conversational chatbots without coding.
+2021
+VB App
+VB is an application with the “Luna” bot and Indonesian text to speech technology with two voice options
+2022
+Wabis Botika
+is a platform to upgrade you whatsapp business to whatsapp business API with masking name and green thick
+</t>
+  </si>
+  <si>
+    <t>Botika teknologi</t>
+  </si>
+  <si>
+    <t>Teknologi apa aja yang ada di Botika?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEXT
+POS Tagging
+Sentence Boundaries
+Text Chunking
+Syntax Analysis
+Language Modeling
+Question Answering
+Intent Classification
+Named Entity Recognition (NER)
+Topic Detection
+Text Summarization
+Text Generation
+Word Tokenization
+TEXT &amp; VOICE 
+Speech Recognition(STT) 
+Speech Synthesizing (TTS) 
+COMPUTER VISION
+OCR 
+Image Classification 
+Face Recognition 
+</t>
+  </si>
+  <si>
+    <t>Competitive Advantage</t>
+  </si>
+  <si>
+    <t>Apa keunggulan Botika dibanding yang lain?</t>
+  </si>
+  <si>
+    <t>Kombinasi Chatbot dan Omni Channel
+Kolaborasi manusia dengan mesin. Chatbot dapat mengeskalasi kasus kepada agen untuk sentuhan manusia dan penyelesaian masalah yang kompleks.
+Teknologi Suara Internal
+Speech To Text dan Text To Voice untuk memungkinkan komunikasi berbasis suara untuk speaker pintar dan telepon.
+Terhubung dengan Sistem yang Ada Melalui API dengan Mulus
+Menghubungkan sistem yang ada ke chatbot untuk bertransaksi dengan pelanggan dan mendapatkan data yang relevan.
+Sangat Dapat Disesuaikan
+Dengan mudah membuat persona chatbot dan karakter suara yang sesuai dengan merek dan target pasar.
+Pengiriman Cepat
+Waktu rata-rata untuk pengembangan khusus hingga rilis versi kurang dari 4 minggu.
+Harga Kompetitif, Layanan Unggul
+NLP dan Pembelajaran Mesin Internal dalam Bahasa Lokal Mesin internal yang dibangun untuk memastikan inovasi cepat dan fleksibilitas dalam melayani pelanggan dalam bahasa mereka.</t>
+  </si>
+  <si>
+    <t>Team Member</t>
+  </si>
+  <si>
+    <t>Siapa aja tim di balik Botika?</t>
+  </si>
+  <si>
+    <t>Ide BOTIKA dimulai pada tanggal 1 September 2016 oleh dua pemuda dari Yogyakarta, Dito Anindita dan Galuh Koco Sadewo.
+Untuk mewujudkan ide ini, mereka juga berkolaborasi dengan Prima Kharisma, Eri Kuncoro, dan Vita Subiyakti untuk membuat terobosan dalam teknologi AI di Indonesia.
+Dengan ini, mereka percaya bahwa teknologi AI mampu menyederhanakan setiap aspek kehidupan manusia.
+Sekarang Botika sudah memiliki 50 karyawan yang tersebar di Yogyakarta dan Jakarta</t>
+  </si>
+  <si>
+    <t>Untuk menjalin kerjasama dan kesempatan investasi</t>
+  </si>
+  <si>
+    <t>Produk Business and Partnership di Botika berfokus pada pembangunan kerja sama strategis dengan berbagai pihak untuk memperluas peluang bisnis dan menciptakan nilai bersama.
+Melalui program ini, Botika membuka kesempatan bagi perusahaan, lembaga, maupun individu untuk menjalin kemitraan bisnis, kolaborasi teknologi, atau kerja sama komersial yang saling menguntungkan.
+Setiap bentuk kerja sama akan disesuaikan dengan kebutuhan dan tujuan masing-masing mitra, dengan fokus pada pengembangan bisnis, inovasi produk, dan peningkatan efisiensi operasional.
+Jika Anda tertarik menjalin kerja sama atau ingin mengeksplorasi peluang kemitraan dan investasi, silakan hubungi kami melalui email di galuh@botika.online</t>
+  </si>
+  <si>
+    <t>Apa saja produk di Botika?</t>
+  </si>
+  <si>
+    <t>Produk produk di botika antara lain, LLM, Digital Human AI (Virtual Avatar), Omnibotika, Voicebotika, Blastika, Chatbotika, Platform, Wabis (Whatsapp Business). Untuk penjelasan produk lebih lanjut silakan kunjungi https://botika.online/product</t>
+  </si>
+  <si>
+    <t>Portofolio Botika</t>
+  </si>
+  <si>
+    <t>Untuk melihat portofolio Botika, silakan kunjungi https://botika.online/. Di sana, terdapat penjelasan singkat mengenai produk-produk kami dan berbagai use case dari tiap klien yang telah menggunakan layanan Botika.</t>
+  </si>
+  <si>
+    <t>berapa SLA yang diperlukan, khususnya untuk perubahan mendadak (misalnya, d</t>
+  </si>
+  <si>
+    <t>Untuk perubahan ini nanti akan berbeda-beda untuk timelinenya bergantung dengan seberapa banyak yang perlu diubah dan apakah masuk ke Mayor, Medium, Minor. Untuk lebih jelasnya dapat mengikuti panduan SLA dibawha ini ;</t>
+  </si>
+  <si>
+    <t>Siapa kamu?
+Kamu itu siapa?
+Perkenalkan dirimu
+Luna siapanya botika</t>
+  </si>
+  <si>
+    <t>SLA-nya gimana tuh kalau ada perubahan?</t>
+  </si>
+  <si>
+    <t>Perkenalkan, saya Luna, asisten virtual dari Botika. Saya siap membantu menjawab pertanyaan seputar produk Botika, mengatasi kendala yang Anda alami, serta menjawab pertanyaan umum lainnya. Jangan ragu untuk bertanya, saya selalu tersedia untuk Anda.</t>
+  </si>
+  <si>
+    <t>Penghargaan Botika
+Pencapaian terbesar Botika</t>
+  </si>
+  <si>
+    <t>Kamu ini siapa sih?</t>
+  </si>
+  <si>
+    <t>Berikut pencapaian terbesar yang telah diraih dan penghargaan industri yang diterima Botika atas solusi AI-nya yang inovatif:
+- 2024 (Microsoft BUILD: AI Day)
+Awards/Achievement: KAI partner for digital human AI
+Products: Superchatbot &amp; Digital Human AI botika: Nilam KAI
+Descriptions: Microsoft Chairman and CEO, Satya Nadella, visited Indonesia to meet with Microsoft partners utilizing AI technology in everyday applications. As part of this visit, Botika was highlighted for its collaboration with Microsoft in developing a digital human AI for KAI, demonstrating the innovative integration of AI into real-world solutions.
+- 2023 (Microsoft Generative AI Champion 2023)
+Awards/Achievement: Microsoft Indonesia Partner Award
+Products: Superchatbot &amp; Digital Human AI Botika
+Descriptions: Reaching New Heights with Generative AI! We are proud to announce that Botika has been named a Generative AI Champion Partner at the FY 24 Microsoft Indonesia Kick Off event, themed 'Empowering Growth and Innovation in Indonesia.' The event, held at Glass House, Ritz Carlton Pacific Place, Jakarta, reaffirms our commitment to driving growth and innovation in the country.The award was presented by Microsoft Indonesia President Director, Darma Simorangkir, to Galuh Koco Sadewo, Co-Founder &amp; CBD of Botika Teknologi. We believe Generative AI will revolutionize the business and communication landscape, and together with Microsoft, we will continue delivering advanced solutions to help Indonesian businesses grow and innovate. A big thank you to the entire Botika team and partners for contributing to this incredible achievement. Let’s move forward towards a brighter, more innovative future!
+- 2021 (Asean ICT)
+Awards/Achievement: Bronze Winner 2021
+Products: Omnibotika
+Descriptions: Bronze Winner 2021. AICTA is an event that recognizes the best ICT works across the ASEAN region, serving as a benchmark for success in terms of innovation and creativity. AICTA offers business opportunities and promotes trade relations, thereby strengthening the technology and informatics sector in ASEAN and internationally. It also serves as a platform to promote the ICT achievements of ASEAN countries on a global scale.
+- 2020 (SXSW (Austin-Texas))
+Awards/Achievement: As Indonesian Representative 2020
+Products: Omnibotika &amp; Chatbotika
+Descriptions: We are proud to have been published in the AI Journal for our innovative use of AI in customer support. Our cutting-edge technology is transforming the way businesses interact with their customers, providing efficient and personalized solutions.
+- 2018 (Telkomsel NextDev)
+Awards/Achievement: 2nd Evangelist 2018
+Products: Omnibotika &amp; Chatbotika
+Descriptions: We are proud to have been published in the AI Journal for our innovative use of AI in customer support. Our cutting-edge technology is transforming the way businesses interact with their customers, providing efficient and personalized solutions.</t>
+  </si>
+  <si>
+    <t>Bagaimana prosedur jika ada perubahan flow di masa depan?</t>
+  </si>
+  <si>
+    <t>Penghargaan apa aja yang pernah diraih Botika?</t>
+  </si>
+  <si>
+    <t>Jika ada perubahan flow bisa melakukan email ke IT analyst atau ke team support kami.</t>
+  </si>
+  <si>
+    <t>Untuk menagih hutang sebaiknya menggunakan produk Botika yang mana?</t>
+  </si>
+  <si>
+    <t>Gimana kalau ada perubahan flow chatbot?</t>
+  </si>
+  <si>
+    <t>Untuk menagih utang, Blastika adalah pilihan yang tepat. Aplikasi ini dirancang khusus untuk melakukan panggilan massal secara otomatis, sehingga sangat efisien untuk menjangkau banyak orang dalam waktu singkat. Dengan Blastika, Anda dapat menyampaikan pesan atau pengingat pembayaran kepada banyak penerima sekaligus, memastikan pesan Anda tersampaikan tanpa harus melakukan panggilan satu per satu. Selain itu, penggunaan Blastika dapat menghemat waktu dan tenaga, serta meningkatkan efektivitas komunikasi bisnis Anda</t>
+  </si>
+  <si>
+    <t>Berapa jumlah flow yang diberikan saat implementasi awal?</t>
+  </si>
+  <si>
+    <t>Produk Botika mana yang cocok buat nagih hutang?</t>
+  </si>
+  <si>
+    <t>Untuk jumlah flow yang diberikan saat implementasi awal ini bergantung pada kesepakatan pada saat pembuatan SOW</t>
+  </si>
+  <si>
+    <t>Apakah LLM bisa digunakan untuk membantu menulis artikel atau laporan?</t>
+  </si>
+  <si>
+    <t>Flow awal implementasi ada berapa?</t>
+  </si>
+  <si>
+    <t>Silakan hubungi tim support kami melalui email di support@botika.online. Kami akan dengan segera memberikan solusi terbaik untuk kebutuhan Anda. Terima kasih atas kepercayaan Anda kepada layanan kami, dan kami menantikan kesempatan untuk membantu Anda lebih lanjut.</t>
+  </si>
+  <si>
+    <t>Competitive Advantage
+Kelebihan/Keunggulan Produk Botika</t>
+  </si>
+  <si>
+    <t>Bisa nggak LLM nulis artikel buat gue?</t>
+  </si>
+  <si>
+    <t>Berikut kelebihan atau keunggulan dari produk Botika:
+- Kombinasi Chatbot dan Omni Channel
+Kolaborasi manusia dengan mesin. Chatbot dapat mengeskalasi kasus kepada agen untuk sentuhan manusia dan penyelesaian masalah yang kompleks.
+- Teknologi Suara Internal
+Speech To Text dan Text To Voice untuk memungkinkan komunikasi berbasis suara untuk speaker pintar dan telepon.
+- Terhubung dengan Sistem yang Ada Melalui API dengan Mulus
+Menghubungkan sistem yang ada ke chatbot untuk bertransaksi dengan pelanggan dan mendapatkan data yang relevan.
+- Sangat Dapat Disesuaikan
+Dengan mudah membuat persona chatbot dan karakter suara yang sesuai dengan merek dan target pasar.
+- Pengiriman Cepat
+Waktu rata-rata untuk pengembangan khusus hingga rilis versi kurang dari 4 minggu.
+- Harga Kompetitif, Layanan Unggul
+NLP dan Pembelajaran Mesin Internal dalam Bahasa Lokal Mesin internal yang dibangun untuk memastikan inovasi cepat dan fleksibilitas dalam melayani pelanggan dalam bahasa mereka.</t>
+  </si>
+  <si>
+    <t>Penawaran KiosK atau Layanan ke Botika</t>
+  </si>
+  <si>
+    <t>Apa aja sih kelebihan Botika?</t>
+  </si>
+  <si>
+    <t>Terkait penawaran ke Botika terkait KiosK atau layanan lainnya, silakan hubungi kami melalui email berikut: To: galuh@botika.online</t>
+  </si>
+  <si>
+    <t>Batasan Karakter untuk Persona</t>
+  </si>
+  <si>
+    <t>Mau penawaran kios atau layanan ke Botika, hubungi siapa?</t>
+  </si>
+  <si>
+    <t>Saat ini, belum ada batasan maksimal karakter yang ditetapkan untuk persona chatbot. Anda dapat memasukkan deskripsi persona sesuai kebutuhan tanpa khawatir tentang batasan karakter. Ini memberikan fleksibilitas dalam mendefinisikan kepribadian dan karakter chatbot Anda dengan lebih detail dan sesuai dengan tujuan penggunaan.</t>
+  </si>
+  <si>
+    <t>Unique user artinya apa ?</t>
+  </si>
+  <si>
+    <t>Ada batasan karakter buat persona chatbot nggak?</t>
+  </si>
+  <si>
+    <t>User yang sudah melakukan chat dalam kurun waktu tertentu biasanya per bulan</t>
+  </si>
+  <si>
+    <t>Permintaan Penambahan Kontrak Total License</t>
+  </si>
+  <si>
+    <t>Unique user itu maksudnya apa sih?</t>
+  </si>
+  <si>
+    <t>Untuk penambahan license agent omnibotika, dapat mengirimkan email ke:
+To: galuh@botika.online</t>
+  </si>
+  <si>
+    <t>bagaimana menjalin kerjasama dan kesempatan investasi?</t>
+  </si>
+  <si>
+    <t>Aku mau tau dong portofolio dari botika</t>
+  </si>
+  <si>
+    <t>Untuk penambahan Permintaan Penambahan Kontrak Total License gimana?</t>
   </si>
 </sst>
 </file>
@@ -105,7 +473,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -115,12 +483,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4CCCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE599"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -160,7 +522,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -187,9 +549,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,209 +880,425 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="B11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="286.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="B12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="247.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="3"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="3"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="3"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="3"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+    <row r="16" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="195.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2"/>
